--- a/case_studies/Free_MPW/2030/technologies.xlsx
+++ b/case_studies/Free_MPW/2030/technologies.xlsx
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>53.53</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>150.99</v>
+        <v>78.39</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -703,25 +703,25 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>946.41</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>946.41</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>135.49</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>184.21</v>
+        <v>1526.74</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>36.8</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>22.37</v>
+        <v>1038.6</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>159.94</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>49.16</v>
+        <v>0</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>23.43</v>
+        <v>0</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -891,16 +891,16 @@
         <v>153.06</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>20.3</v>
+        <v>25.09</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1369.36</v>
+        <v>112.05</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1369.36</v>
+        <v>112.05</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
@@ -909,13 +909,13 @@
         <v>31.96</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>63.68</v>
+        <v>2281.75</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>43.32</v>
+        <v>1565.26</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>231.42</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>27.91</v>
+        <v>34.5</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -982,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>108.43</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>241.1</v>
+        <v>229.84</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>148.52</v>
+        <v>148.53</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0</v>
@@ -1003,16 +1003,16 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>20.11</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>352.18</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>0</v>
+        <v>225.9</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>125.97</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>55.06</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>141.59</v>
+        <v>46.83</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1091,25 +1091,25 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>565.33</v>
+        <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>565.33</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>139.37</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>139.37</v>
+        <v>875.42</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>37.86</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0</v>
+        <v>595.53</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>37.86</v>
+        <v>0</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>15.33</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.57</v>
+        <v>10.54</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.8</v>
+        <v>39.29</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1218,7 +1218,7 @@
         <v>1.43</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.18</v>
+        <v>10.15</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>65.58</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>161.65</v>
+        <v>54.11</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1285,25 +1285,25 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>653.27</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>653.27</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>165.99</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>219.11</v>
+        <v>680.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>45.09</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>36.14</v>
+        <v>462.6</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>110.4</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>45.09</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>
